--- a/case_studies/test/technologies.xlsx
+++ b/case_studies/test/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1270D1-ED4F-4F81-898B-F2973B3343A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD77C36-9965-40FD-AF0E-F581D89EC9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>cluster</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>DAC_Adsorption</t>
+  </si>
+  <si>
+    <t>MEA_medium</t>
   </si>
 </sst>
 </file>
@@ -436,10 +439,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,8 +515,11 @@
       <c r="X1" t="s">
         <v>30</v>
       </c>
+      <c r="Y1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -586,8 +592,11 @@
       <c r="X2">
         <v>0</v>
       </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -660,8 +669,11 @@
       <c r="X3">
         <v>0</v>
       </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -734,8 +746,11 @@
       <c r="X4">
         <v>0</v>
       </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -808,8 +823,11 @@
       <c r="X5">
         <v>0</v>
       </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -882,8 +900,11 @@
       <c r="X6">
         <v>0</v>
       </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -956,8 +977,11 @@
       <c r="X7">
         <v>0</v>
       </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1028,6 +1052,9 @@
         <v>0</v>
       </c>
       <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <v>0</v>
       </c>
     </row>
@@ -1038,10 +1065,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1114,8 +1141,11 @@
       <c r="X1" t="s">
         <v>30</v>
       </c>
+      <c r="Y1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1147,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -1159,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1171,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -1188,8 +1218,11 @@
       <c r="X2">
         <v>0</v>
       </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1221,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1233,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1245,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1262,8 +1295,11 @@
       <c r="X3">
         <v>0</v>
       </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1295,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -1307,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1319,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -1336,8 +1372,11 @@
       <c r="X4">
         <v>0</v>
       </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1369,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1381,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1393,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -1410,8 +1449,11 @@
       <c r="X5">
         <v>0</v>
       </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1443,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -1455,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1467,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1484,8 +1526,11 @@
       <c r="X6">
         <v>0</v>
       </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1517,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1529,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1541,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1558,8 +1603,11 @@
       <c r="X7">
         <v>0</v>
       </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1591,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1603,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1615,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1630,6 +1678,9 @@
         <v>0</v>
       </c>
       <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <v>0</v>
       </c>
     </row>
